--- a/project/outputs_xlsx_solution/test_new3.4-wide-NB-1.xlsx
+++ b/project/outputs_xlsx_solution/test_new3.4-wide-NB-1.xlsx
@@ -119,6 +119,9 @@
     <t>RS Stall</t>
   </si>
   <si>
+    <t>ROB Stall</t>
+  </si>
+  <si>
     <t>fadd F2, F2, F4</t>
   </si>
   <si>
@@ -150,9 +153,6 @@
   </si>
   <si>
     <t>Reservation Station Stall (stalled because reservation stations are full)</t>
-  </si>
-  <si>
-    <t>ROB Stall</t>
   </si>
   <si>
     <t>Reorder Buffer Stall (stalled because the ROB is full)</t>
@@ -967,7 +967,7 @@
         <v>9</v>
       </c>
       <c r="H10" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I10" t="s">
         <v>15</v>
@@ -1082,9 +1082,6 @@
         <v>26</v>
       </c>
       <c r="Z12" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA12" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1114,7 +1111,19 @@
         <v>26</v>
       </c>
       <c r="V13" t="s">
-        <v>19</v>
+        <v>26</v>
+      </c>
+      <c r="W13" t="s">
+        <v>26</v>
+      </c>
+      <c r="X13" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>26</v>
       </c>
       <c r="AA13" t="s">
         <v>20</v>
@@ -1197,7 +1206,7 @@
       <c r="O16" t="s">
         <v>19</v>
       </c>
-      <c r="AB16" t="s">
+      <c r="AA16" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1265,9 +1274,6 @@
         <v>26</v>
       </c>
       <c r="Y18" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z18" t="s">
         <v>19</v>
       </c>
       <c r="AB18" t="s">
@@ -1302,6 +1308,9 @@
       <c r="U19" t="s">
         <v>21</v>
       </c>
+      <c r="Z19" t="s">
+        <v>14</v>
+      </c>
       <c r="AA19" t="s">
         <v>14</v>
       </c>
@@ -1312,15 +1321,12 @@
         <v>14</v>
       </c>
       <c r="AD19" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="AE19" t="s">
         <v>26</v>
       </c>
       <c r="AF19" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG19" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1343,16 +1349,46 @@
       <c r="U20" t="s">
         <v>21</v>
       </c>
+      <c r="Y20" t="s">
+        <v>14</v>
+      </c>
       <c r="Z20" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="AA20" t="s">
         <v>26</v>
       </c>
       <c r="AB20" t="s">
-        <v>19</v>
+        <v>26</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>26</v>
       </c>
       <c r="AG20" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>26</v>
+      </c>
+      <c r="AK20" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL20" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1373,15 +1409,12 @@
         <v>9</v>
       </c>
       <c r="U21" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="V21" t="s">
-        <v>14</v>
-      </c>
-      <c r="W21" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG21" t="s">
+        <v>19</v>
+      </c>
+      <c r="AL21" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1402,18 +1435,15 @@
         <v>9</v>
       </c>
       <c r="U22" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="V22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W22" t="s">
-        <v>14</v>
-      </c>
-      <c r="X22" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG22" t="s">
+        <v>19</v>
+      </c>
+      <c r="AL22" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1436,13 +1466,13 @@
       <c r="V23" t="s">
         <v>21</v>
       </c>
+      <c r="W23" t="s">
+        <v>14</v>
+      </c>
       <c r="X23" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH23" t="s">
+        <v>19</v>
+      </c>
+      <c r="AL23" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1465,13 +1495,13 @@
       <c r="V24" t="s">
         <v>21</v>
       </c>
+      <c r="X24" t="s">
+        <v>14</v>
+      </c>
       <c r="Y24" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z24" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH24" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM24" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1494,6 +1524,9 @@
       <c r="V25" t="s">
         <v>21</v>
       </c>
+      <c r="Y25" t="s">
+        <v>14</v>
+      </c>
       <c r="Z25" t="s">
         <v>14</v>
       </c>
@@ -1501,7 +1534,7 @@
         <v>14</v>
       </c>
       <c r="AB25" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="AC25" t="s">
         <v>26</v>
@@ -1510,12 +1543,9 @@
         <v>26</v>
       </c>
       <c r="AE25" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AH25" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM25" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1548,10 +1578,10 @@
         <v>27</v>
       </c>
       <c r="Z26" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA26" t="s">
-        <v>21</v>
+        <v>21</v>
+      </c>
+      <c r="AF26" t="s">
+        <v>14</v>
       </c>
       <c r="AG26" t="s">
         <v>14</v>
@@ -1563,13 +1593,7 @@
         <v>14</v>
       </c>
       <c r="AJ26" t="s">
-        <v>14</v>
-      </c>
-      <c r="AK26" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL26" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AM26" t="s">
         <v>20</v>
@@ -1591,16 +1615,19 @@
       <c r="S27" t="s">
         <v>9</v>
       </c>
+      <c r="Z27" t="s">
+        <v>27</v>
+      </c>
       <c r="AA27" t="s">
         <v>21</v>
       </c>
+      <c r="AE27" t="s">
+        <v>14</v>
+      </c>
       <c r="AF27" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="AG27" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH27" t="s">
         <v>19</v>
       </c>
       <c r="AM27" t="s">
@@ -1624,15 +1651,12 @@
         <v>9</v>
       </c>
       <c r="AA28" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AB28" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC28" t="s">
-        <v>19</v>
-      </c>
-      <c r="AM28" t="s">
+        <v>19</v>
+      </c>
+      <c r="AN28" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1653,18 +1677,15 @@
         <v>9</v>
       </c>
       <c r="AA29" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AB29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC29" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD29" t="s">
-        <v>19</v>
-      </c>
-      <c r="AM29" t="s">
+        <v>19</v>
+      </c>
+      <c r="AN29" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1684,13 +1705,13 @@
       <c r="T30" t="s">
         <v>9</v>
       </c>
-      <c r="AB30" t="s">
-        <v>21</v>
+      <c r="AA30" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>14</v>
       </c>
       <c r="AD30" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE30" t="s">
         <v>19</v>
       </c>
       <c r="AN30" t="s">
@@ -1716,10 +1737,10 @@
       <c r="AB31" t="s">
         <v>21</v>
       </c>
+      <c r="AD31" t="s">
+        <v>14</v>
+      </c>
       <c r="AE31" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF31" t="s">
         <v>19</v>
       </c>
       <c r="AN31" t="s">
@@ -1745,6 +1766,9 @@
       <c r="AB32" t="s">
         <v>21</v>
       </c>
+      <c r="AE32" t="s">
+        <v>14</v>
+      </c>
       <c r="AF32" t="s">
         <v>14</v>
       </c>
@@ -1752,21 +1776,12 @@
         <v>14</v>
       </c>
       <c r="AH32" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="AI32" t="s">
-        <v>26</v>
-      </c>
-      <c r="AJ32" t="s">
-        <v>26</v>
-      </c>
-      <c r="AK32" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL32" t="s">
-        <v>19</v>
-      </c>
-      <c r="AN32" t="s">
+        <v>19</v>
+      </c>
+      <c r="AO32" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1799,22 +1814,28 @@
         <v>27</v>
       </c>
       <c r="AF33" t="s">
-        <v>27</v>
-      </c>
-      <c r="AG33" t="s">
-        <v>21</v>
+        <v>21</v>
+      </c>
+      <c r="AJ33" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK33" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL33" t="s">
+        <v>14</v>
       </c>
       <c r="AM33" t="s">
         <v>14</v>
       </c>
       <c r="AN33" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="AO33" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="AP33" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="AQ33" t="s">
         <v>26</v>
@@ -1842,16 +1863,19 @@
       <c r="U34" t="s">
         <v>9</v>
       </c>
+      <c r="AF34" t="s">
+        <v>27</v>
+      </c>
       <c r="AG34" t="s">
         <v>21</v>
       </c>
-      <c r="AL34" t="s">
-        <v>14</v>
-      </c>
-      <c r="AM34" t="s">
-        <v>26</v>
-      </c>
-      <c r="AN34" t="s">
+      <c r="AI34" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ34" t="s">
+        <v>26</v>
+      </c>
+      <c r="AK34" t="s">
         <v>19</v>
       </c>
       <c r="AS34" t="s">
@@ -1875,12 +1899,9 @@
         <v>9</v>
       </c>
       <c r="AG35" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AH35" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI35" t="s">
         <v>19</v>
       </c>
       <c r="AS35" t="s">
@@ -1904,15 +1925,24 @@
         <v>9</v>
       </c>
       <c r="AG36" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AH36" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="AI36" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AJ36" t="s">
+        <v>28</v>
+      </c>
+      <c r="AK36" t="s">
+        <v>28</v>
+      </c>
+      <c r="AL36" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM36" t="s">
         <v>19</v>
       </c>
       <c r="AS36" t="s">
@@ -1935,13 +1965,13 @@
       <c r="V37" t="s">
         <v>9</v>
       </c>
-      <c r="AH37" t="s">
-        <v>21</v>
-      </c>
-      <c r="AJ37" t="s">
-        <v>14</v>
-      </c>
-      <c r="AK37" t="s">
+      <c r="AL37" t="s">
+        <v>21</v>
+      </c>
+      <c r="AM37" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN37" t="s">
         <v>19</v>
       </c>
       <c r="AT37" t="s">
@@ -1964,13 +1994,13 @@
       <c r="V38" t="s">
         <v>9</v>
       </c>
-      <c r="AH38" t="s">
-        <v>21</v>
-      </c>
-      <c r="AK38" t="s">
-        <v>14</v>
-      </c>
       <c r="AL38" t="s">
+        <v>21</v>
+      </c>
+      <c r="AN38" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO38" t="s">
         <v>19</v>
       </c>
       <c r="AT38" t="s">
@@ -1993,9 +2023,6 @@
       <c r="W39" t="s">
         <v>9</v>
       </c>
-      <c r="AH39" t="s">
-        <v>21</v>
-      </c>
       <c r="AL39" t="s">
         <v>14</v>
       </c>
@@ -2037,21 +2064,6 @@
       <c r="W40" t="s">
         <v>9</v>
       </c>
-      <c r="AH40" t="s">
-        <v>27</v>
-      </c>
-      <c r="AI40" t="s">
-        <v>27</v>
-      </c>
-      <c r="AJ40" t="s">
-        <v>27</v>
-      </c>
-      <c r="AK40" t="s">
-        <v>27</v>
-      </c>
-      <c r="AL40" t="s">
-        <v>27</v>
-      </c>
       <c r="AM40" t="s">
         <v>21</v>
       </c>
@@ -2119,11 +2131,11 @@
       <c r="V42" t="s">
         <v>5</v>
       </c>
-      <c r="AA42" t="s">
+      <c r="Z42" t="s">
         <v>9</v>
       </c>
       <c r="AM42" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AN42" t="s">
         <v>14</v>
@@ -2152,7 +2164,7 @@
         <v>9</v>
       </c>
       <c r="AM43" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AN43" t="s">
         <v>15</v>
@@ -2233,7 +2245,7 @@
         <v>64</v>
       </c>
       <c r="C46" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR46" t="s">
         <v>5</v>
@@ -2300,7 +2312,7 @@
         <v>72</v>
       </c>
       <c r="C48" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR48" t="s">
         <v>5</v>
@@ -2332,7 +2344,7 @@
         <v>76</v>
       </c>
       <c r="C49" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AR49" t="s">
         <v>5</v>
@@ -2352,7 +2364,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52">
@@ -2360,7 +2372,7 @@
         <v>5</v>
       </c>
       <c r="B52" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="53">
@@ -2368,7 +2380,7 @@
         <v>9</v>
       </c>
       <c r="B53" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54">
@@ -2376,7 +2388,7 @@
         <v>21</v>
       </c>
       <c r="B54" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="55">
@@ -2384,7 +2396,7 @@
         <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56">
@@ -2392,7 +2404,7 @@
         <v>19</v>
       </c>
       <c r="B56" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="57">
@@ -2400,7 +2412,7 @@
         <v>20</v>
       </c>
       <c r="B57" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="58">
@@ -2408,12 +2420,12 @@
         <v>27</v>
       </c>
       <c r="B58" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B59" t="s">
         <v>40</v>
